--- a/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v12.xlsx
+++ b/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\docs\migration-orders\davin-operational-manual\antigravity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C509DE-C536-4082-99A3-6FC3A0AEBAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF03C5E-0148-4BFE-B05C-8FB4EAF10E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7982,57 +7982,6 @@
     <xf numFmtId="0" fontId="0" fillId="26" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8048,6 +7997,57 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11784,16 +11784,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="156" t="s">
         <v>2106</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="110" t="s">
@@ -13058,31 +13058,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="136" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
     </row>
     <row r="2" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="133" t="s">
+      <c r="A2" s="145" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
     </row>
     <row r="4" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="129" t="s">
+      <c r="A4" s="144" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
     </row>
     <row r="5" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="68" t="s">
@@ -13136,13 +13136,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="138" t="s">
+      <c r="A9" s="143" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="130"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
+      <c r="B9" s="137"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="137"/>
     </row>
     <row r="10" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="68" t="s">
@@ -13379,11 +13379,11 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="130"/>
-      <c r="B24" s="130"/>
-      <c r="C24" s="130"/>
-      <c r="D24" s="130"/>
-      <c r="E24" s="130"/>
+      <c r="A24" s="137"/>
+      <c r="B24" s="137"/>
+      <c r="C24" s="137"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
     </row>
     <row r="25" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="77" t="s">
@@ -13394,51 +13394,51 @@
       <c r="A26" s="68" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="137" t="s">
+      <c r="B26" s="141" t="s">
         <v>163</v>
       </c>
-      <c r="C26" s="132"/>
-      <c r="D26" s="137"/>
-      <c r="E26" s="132"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="140"/>
     </row>
     <row r="27" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="73" t="s">
         <v>164</v>
       </c>
-      <c r="B27" s="131" t="s">
+      <c r="B27" s="142" t="s">
         <v>165</v>
       </c>
-      <c r="C27" s="132"/>
-      <c r="D27" s="131" t="s">
+      <c r="C27" s="140"/>
+      <c r="D27" s="142" t="s">
         <v>166</v>
       </c>
-      <c r="E27" s="132"/>
+      <c r="E27" s="140"/>
     </row>
     <row r="28" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="73" t="s">
         <v>167</v>
       </c>
-      <c r="B28" s="131" t="s">
+      <c r="B28" s="142" t="s">
         <v>168</v>
       </c>
-      <c r="C28" s="132"/>
-      <c r="D28" s="131" t="s">
+      <c r="C28" s="140"/>
+      <c r="D28" s="142" t="s">
         <v>169</v>
       </c>
-      <c r="E28" s="132"/>
+      <c r="E28" s="140"/>
     </row>
     <row r="29" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="73" t="s">
         <v>170</v>
       </c>
-      <c r="B29" s="131" t="s">
+      <c r="B29" s="142" t="s">
         <v>171</v>
       </c>
-      <c r="C29" s="132"/>
-      <c r="D29" s="131" t="s">
+      <c r="C29" s="140"/>
+      <c r="D29" s="142" t="s">
         <v>172</v>
       </c>
-      <c r="E29" s="132"/>
+      <c r="E29" s="140"/>
     </row>
     <row r="30" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="73" t="s">
@@ -13454,11 +13454,11 @@
       <c r="E30" s="78"/>
     </row>
     <row r="31" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="130"/>
-      <c r="B31" s="130"/>
-      <c r="C31" s="130"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="130"/>
+      <c r="A31" s="137"/>
+      <c r="B31" s="137"/>
+      <c r="C31" s="137"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="137"/>
     </row>
     <row r="32" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="80" t="s">
@@ -13526,13 +13526,13 @@
       <c r="E36" s="70"/>
     </row>
     <row r="37" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="135" t="s">
+      <c r="A37" s="138" t="s">
         <v>192</v>
       </c>
-      <c r="B37" s="136"/>
-      <c r="C37" s="136"/>
-      <c r="D37" s="136"/>
-      <c r="E37" s="132"/>
+      <c r="B37" s="139"/>
+      <c r="C37" s="139"/>
+      <c r="D37" s="139"/>
+      <c r="E37" s="140"/>
     </row>
     <row r="38" spans="1:5" ht="230.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="79" t="s">
@@ -14322,76 +14322,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="151" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
     </row>
     <row r="2" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="141" t="s">
+      <c r="A2" s="146" t="s">
         <v>309</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
     </row>
     <row r="4" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="152" t="s">
         <v>310</v>
       </c>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
     </row>
     <row r="5" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="141" t="s">
+      <c r="A5" s="146" t="s">
         <v>311</v>
       </c>
-      <c r="B5" s="130"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
+      <c r="B5" s="137"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="137"/>
     </row>
     <row r="6" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="141" t="s">
+      <c r="A6" s="146" t="s">
         <v>312</v>
       </c>
-      <c r="B6" s="130"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
-      <c r="E6" s="130"/>
+      <c r="B6" s="137"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="137"/>
     </row>
     <row r="7" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="141" t="s">
+      <c r="A7" s="146" t="s">
         <v>313</v>
       </c>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
+      <c r="B7" s="137"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
     </row>
     <row r="8" spans="1:5" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="141" t="s">
+      <c r="A8" s="146" t="s">
         <v>314</v>
       </c>
-      <c r="B8" s="130"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
     </row>
     <row r="10" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="144" t="s">
+      <c r="A10" s="148" t="s">
         <v>315</v>
       </c>
-      <c r="B10" s="130"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
     </row>
     <row r="11" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="61" t="s">
@@ -14581,11 +14581,11 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="142"/>
-      <c r="B22" s="136"/>
-      <c r="C22" s="136"/>
-      <c r="D22" s="136"/>
-      <c r="E22" s="132"/>
+      <c r="A22" s="147"/>
+      <c r="B22" s="139"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="140"/>
     </row>
     <row r="23" spans="1:5" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="82" t="s">
@@ -14593,11 +14593,11 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="130"/>
-      <c r="B24" s="130"/>
-      <c r="C24" s="130"/>
-      <c r="D24" s="130"/>
-      <c r="E24" s="130"/>
+      <c r="A24" s="137"/>
+      <c r="B24" s="137"/>
+      <c r="C24" s="137"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
     </row>
     <row r="25" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="59" t="s">
@@ -14639,22 +14639,22 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="145" t="s">
+      <c r="A28" s="149" t="s">
         <v>344</v>
       </c>
-      <c r="B28" s="136"/>
-      <c r="C28" s="136"/>
-      <c r="D28" s="136"/>
-      <c r="E28" s="132"/>
+      <c r="B28" s="139"/>
+      <c r="C28" s="139"/>
+      <c r="D28" s="139"/>
+      <c r="E28" s="140"/>
     </row>
     <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="141" t="s">
+      <c r="A29" s="146" t="s">
         <v>345</v>
       </c>
-      <c r="B29" s="130"/>
-      <c r="C29" s="130"/>
-      <c r="D29" s="130"/>
-      <c r="E29" s="130"/>
+      <c r="B29" s="137"/>
+      <c r="C29" s="137"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="137"/>
     </row>
     <row r="30" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="82" t="s">
@@ -14662,11 +14662,11 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="130"/>
-      <c r="B31" s="130"/>
-      <c r="C31" s="130"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="130"/>
+      <c r="A31" s="137"/>
+      <c r="B31" s="137"/>
+      <c r="C31" s="137"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="137"/>
     </row>
     <row r="32" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="83" t="s">
@@ -14759,11 +14759,11 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="130"/>
-      <c r="B38" s="130"/>
-      <c r="C38" s="130"/>
-      <c r="D38" s="130"/>
-      <c r="E38" s="130"/>
+      <c r="A38" s="137"/>
+      <c r="B38" s="137"/>
+      <c r="C38" s="137"/>
+      <c r="D38" s="137"/>
+      <c r="E38" s="137"/>
     </row>
     <row r="39" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="84" t="s">
@@ -14774,67 +14774,67 @@
       <c r="A40" s="61" t="s">
         <v>366</v>
       </c>
-      <c r="B40" s="139" t="s">
+      <c r="B40" s="150" t="s">
         <v>367</v>
       </c>
-      <c r="C40" s="136"/>
-      <c r="D40" s="136"/>
-      <c r="E40" s="132"/>
+      <c r="C40" s="139"/>
+      <c r="D40" s="139"/>
+      <c r="E40" s="140"/>
     </row>
     <row r="41" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="62" t="s">
         <v>368</v>
       </c>
-      <c r="B41" s="131" t="s">
+      <c r="B41" s="142" t="s">
         <v>369</v>
       </c>
-      <c r="C41" s="136"/>
-      <c r="D41" s="136"/>
-      <c r="E41" s="132"/>
+      <c r="C41" s="139"/>
+      <c r="D41" s="139"/>
+      <c r="E41" s="140"/>
     </row>
     <row r="42" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="62" t="s">
         <v>370</v>
       </c>
-      <c r="B42" s="131" t="s">
+      <c r="B42" s="142" t="s">
         <v>371</v>
       </c>
-      <c r="C42" s="136"/>
-      <c r="D42" s="136"/>
-      <c r="E42" s="132"/>
+      <c r="C42" s="139"/>
+      <c r="D42" s="139"/>
+      <c r="E42" s="140"/>
     </row>
     <row r="43" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="62" t="s">
         <v>372</v>
       </c>
-      <c r="B43" s="131" t="s">
+      <c r="B43" s="142" t="s">
         <v>373</v>
       </c>
-      <c r="C43" s="136"/>
-      <c r="D43" s="136"/>
-      <c r="E43" s="132"/>
+      <c r="C43" s="139"/>
+      <c r="D43" s="139"/>
+      <c r="E43" s="140"/>
     </row>
     <row r="44" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="62" t="s">
         <v>374</v>
       </c>
-      <c r="B44" s="131" t="s">
+      <c r="B44" s="142" t="s">
         <v>375</v>
       </c>
-      <c r="C44" s="136"/>
-      <c r="D44" s="136"/>
-      <c r="E44" s="132"/>
+      <c r="C44" s="139"/>
+      <c r="D44" s="139"/>
+      <c r="E44" s="140"/>
     </row>
     <row r="45" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="62" t="s">
         <v>376</v>
       </c>
-      <c r="B45" s="131" t="s">
+      <c r="B45" s="142" t="s">
         <v>377</v>
       </c>
-      <c r="C45" s="136"/>
-      <c r="D45" s="136"/>
-      <c r="E45" s="132"/>
+      <c r="C45" s="139"/>
+      <c r="D45" s="139"/>
+      <c r="E45" s="140"/>
     </row>
     <row r="46" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="62" t="s">
@@ -14848,11 +14848,11 @@
       <c r="E46" s="78"/>
     </row>
     <row r="47" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="130"/>
-      <c r="B47" s="130"/>
-      <c r="C47" s="130"/>
-      <c r="D47" s="130"/>
-      <c r="E47" s="130"/>
+      <c r="A47" s="137"/>
+      <c r="B47" s="137"/>
+      <c r="C47" s="137"/>
+      <c r="D47" s="137"/>
+      <c r="E47" s="137"/>
     </row>
     <row r="48" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="83" t="s">
@@ -14927,6 +14927,14 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A8:E8"/>
@@ -14940,14 +14948,6 @@
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="A4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14968,20 +14968,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="153" t="s">
         <v>393</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
     </row>
     <row r="2" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="141" t="s">
+      <c r="A2" s="146" t="s">
         <v>394</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
     </row>
     <row r="4" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="52" t="s">
@@ -15040,44 +15040,44 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="147" t="s">
+      <c r="A8" s="154" t="s">
         <v>411</v>
       </c>
-      <c r="B8" s="130"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="130"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
     </row>
     <row r="9" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="141" t="s">
+      <c r="A9" s="146" t="s">
         <v>412</v>
       </c>
-      <c r="B9" s="130"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
+      <c r="B9" s="137"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
     </row>
     <row r="10" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="141" t="s">
+      <c r="A10" s="146" t="s">
         <v>413</v>
       </c>
-      <c r="B10" s="130"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="130"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
     </row>
     <row r="11" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="141" t="s">
+      <c r="A11" s="146" t="s">
         <v>414</v>
       </c>
-      <c r="B11" s="130"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
     </row>
     <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="147" t="s">
+      <c r="A13" s="154" t="s">
         <v>415</v>
       </c>
-      <c r="B13" s="130"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
     </row>
     <row r="14" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="52" t="s">
@@ -15164,60 +15164,60 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="147" t="s">
+      <c r="A21" s="154" t="s">
         <v>439</v>
       </c>
-      <c r="B21" s="130"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="130"/>
+      <c r="B21" s="137"/>
+      <c r="C21" s="137"/>
+      <c r="D21" s="137"/>
     </row>
     <row r="22" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="133" t="s">
+      <c r="A22" s="145" t="s">
         <v>440</v>
       </c>
-      <c r="B22" s="130"/>
-      <c r="C22" s="130"/>
-      <c r="D22" s="130"/>
+      <c r="B22" s="137"/>
+      <c r="C22" s="137"/>
+      <c r="D22" s="137"/>
     </row>
     <row r="23" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="133" t="s">
+      <c r="A23" s="145" t="s">
         <v>441</v>
       </c>
-      <c r="B23" s="130"/>
-      <c r="C23" s="130"/>
-      <c r="D23" s="130"/>
+      <c r="B23" s="137"/>
+      <c r="C23" s="137"/>
+      <c r="D23" s="137"/>
     </row>
     <row r="24" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="133" t="s">
+      <c r="A24" s="145" t="s">
         <v>442</v>
       </c>
-      <c r="B24" s="130"/>
-      <c r="C24" s="130"/>
-      <c r="D24" s="130"/>
+      <c r="B24" s="137"/>
+      <c r="C24" s="137"/>
+      <c r="D24" s="137"/>
     </row>
     <row r="25" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="133" t="s">
+      <c r="A25" s="145" t="s">
         <v>443</v>
       </c>
-      <c r="B25" s="130"/>
-      <c r="C25" s="130"/>
-      <c r="D25" s="130"/>
+      <c r="B25" s="137"/>
+      <c r="C25" s="137"/>
+      <c r="D25" s="137"/>
     </row>
     <row r="26" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="133" t="s">
+      <c r="A26" s="145" t="s">
         <v>444</v>
       </c>
-      <c r="B26" s="130"/>
-      <c r="C26" s="130"/>
-      <c r="D26" s="130"/>
+      <c r="B26" s="137"/>
+      <c r="C26" s="137"/>
+      <c r="D26" s="137"/>
     </row>
     <row r="27" spans="1:4" ht="32.049999999999997" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="133" t="s">
+      <c r="A27" s="145" t="s">
         <v>445</v>
       </c>
-      <c r="B27" s="130"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="130"/>
+      <c r="B27" s="137"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -15324,22 +15324,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.05" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="153" t="s">
         <v>462</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
     </row>
     <row r="2" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="141" t="s">
+      <c r="A2" s="146" t="s">
         <v>463</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
     </row>
     <row r="4" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="52" t="s">
@@ -15495,13 +15495,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="147" t="s">
+      <c r="A14" s="154" t="s">
         <v>506</v>
       </c>
-      <c r="B14" s="130"/>
-      <c r="C14" s="130"/>
-      <c r="D14" s="130"/>
-      <c r="E14" s="130"/>
+      <c r="B14" s="137"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
     </row>
     <row r="15" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="52" t="s">
@@ -15657,49 +15657,49 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="148" t="s">
+      <c r="A25" s="155" t="s">
         <v>548</v>
       </c>
-      <c r="B25" s="130"/>
-      <c r="C25" s="130"/>
-      <c r="D25" s="130"/>
-      <c r="E25" s="130"/>
+      <c r="B25" s="137"/>
+      <c r="C25" s="137"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
     </row>
     <row r="26" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="141" t="s">
+      <c r="A26" s="146" t="s">
         <v>549</v>
       </c>
-      <c r="B26" s="130"/>
-      <c r="C26" s="130"/>
-      <c r="D26" s="130"/>
-      <c r="E26" s="130"/>
+      <c r="B26" s="137"/>
+      <c r="C26" s="137"/>
+      <c r="D26" s="137"/>
+      <c r="E26" s="137"/>
     </row>
     <row r="27" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="141" t="s">
+      <c r="A27" s="146" t="s">
         <v>550</v>
       </c>
-      <c r="B27" s="130"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="130"/>
-      <c r="E27" s="130"/>
+      <c r="B27" s="137"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="137"/>
     </row>
     <row r="28" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="141" t="s">
+      <c r="A28" s="146" t="s">
         <v>551</v>
       </c>
-      <c r="B28" s="130"/>
-      <c r="C28" s="130"/>
-      <c r="D28" s="130"/>
-      <c r="E28" s="130"/>
+      <c r="B28" s="137"/>
+      <c r="C28" s="137"/>
+      <c r="D28" s="137"/>
+      <c r="E28" s="137"/>
     </row>
     <row r="29" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="141" t="s">
+      <c r="A29" s="146" t="s">
         <v>552</v>
       </c>
-      <c r="B29" s="130"/>
-      <c r="C29" s="130"/>
-      <c r="D29" s="130"/>
-      <c r="E29" s="130"/>
+      <c r="B29" s="137"/>
+      <c r="C29" s="137"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -25270,105 +25270,105 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="88" spans="1:18" s="156" customFormat="1" ht="166.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="150">
+    <row r="88" spans="1:18" s="33" customFormat="1" ht="166.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="29">
         <v>87</v>
       </c>
-      <c r="B88" s="151" t="s">
+      <c r="B88" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="C88" s="152" t="s">
+      <c r="C88" s="35" t="s">
         <v>1144</v>
       </c>
-      <c r="D88" s="153" t="s">
+      <c r="D88" s="31" t="s">
         <v>567</v>
       </c>
-      <c r="E88" s="154"/>
-      <c r="F88" s="155" t="s">
+      <c r="E88" s="30"/>
+      <c r="F88" s="32" t="s">
         <v>1829</v>
       </c>
-      <c r="G88" s="155" t="s">
+      <c r="G88" s="32" t="s">
         <v>1830</v>
       </c>
-      <c r="H88" s="155" t="s">
+      <c r="H88" s="32" t="s">
         <v>1432</v>
       </c>
-      <c r="I88" s="155" t="s">
-        <v>1424</v>
-      </c>
-      <c r="J88" s="155" t="s">
+      <c r="I88" s="32" t="s">
+        <v>1424</v>
+      </c>
+      <c r="J88" s="32" t="s">
         <v>1433</v>
       </c>
-      <c r="K88" s="155" t="s">
+      <c r="K88" s="32" t="s">
         <v>1831</v>
       </c>
-      <c r="L88" s="153"/>
-      <c r="M88" s="153"/>
-      <c r="N88" s="155" t="s">
+      <c r="L88" s="31"/>
+      <c r="M88" s="31"/>
+      <c r="N88" s="32" t="s">
         <v>1428</v>
       </c>
-      <c r="O88" s="155" t="s">
-        <v>1424</v>
-      </c>
-      <c r="P88" s="155" t="s">
-        <v>1424</v>
-      </c>
-      <c r="Q88" s="155" t="s">
+      <c r="O88" s="32" t="s">
+        <v>1424</v>
+      </c>
+      <c r="P88" s="32" t="s">
+        <v>1424</v>
+      </c>
+      <c r="Q88" s="32" t="s">
         <v>1832</v>
       </c>
-      <c r="R88" s="155" t="s">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="29">
+      <c r="R88" s="32" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" s="135" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="129">
         <v>88</v>
       </c>
-      <c r="B89" s="14" t="s">
+      <c r="B89" s="130" t="s">
         <v>1190</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" s="131" t="s">
         <v>1191</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="132" t="s">
         <v>580</v>
       </c>
-      <c r="E89" s="13" t="s">
+      <c r="E89" s="133" t="s">
         <v>1855</v>
       </c>
-      <c r="F89" s="16" t="s">
+      <c r="F89" s="134" t="s">
         <v>1856</v>
       </c>
-      <c r="G89" s="16" t="s">
+      <c r="G89" s="134" t="s">
         <v>1857</v>
       </c>
-      <c r="H89" s="16" t="s">
+      <c r="H89" s="134" t="s">
         <v>1432</v>
       </c>
-      <c r="I89" s="16"/>
-      <c r="J89" s="16" t="s">
+      <c r="I89" s="134"/>
+      <c r="J89" s="134" t="s">
         <v>1433</v>
       </c>
-      <c r="K89" s="16" t="s">
+      <c r="K89" s="134" t="s">
         <v>1858</v>
       </c>
-      <c r="L89" s="3"/>
-      <c r="M89" s="3" t="s">
+      <c r="L89" s="132"/>
+      <c r="M89" s="132" t="s">
         <v>1550</v>
       </c>
-      <c r="N89" s="16" t="s">
+      <c r="N89" s="134" t="s">
         <v>1428</v>
       </c>
-      <c r="O89" s="16" t="s">
+      <c r="O89" s="134" t="s">
         <v>1620</v>
       </c>
-      <c r="P89" s="16" t="s">
+      <c r="P89" s="134" t="s">
         <v>1859</v>
       </c>
-      <c r="Q89" s="16" t="s">
+      <c r="Q89" s="134" t="s">
         <v>1860</v>
       </c>
-      <c r="R89" s="16"/>
+      <c r="R89" s="134"/>
     </row>
     <row r="90" spans="1:18" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="29">

--- a/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v12.xlsx
+++ b/docs/migration-orders/davin-operational-manual/antigravity/migration-process-handbook-antigravity-v12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\docs\migration-orders\davin-operational-manual\antigravity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9857C40E-78D2-4F56-9C93-1A5521258C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B67A08-A85D-4E76-B5F1-F588E9F78AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7703,7 +7703,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -8108,22 +8108,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -25604,979 +25607,979 @@
       </c>
       <c r="R91" s="156"/>
     </row>
-    <row r="92" spans="1:18" s="165" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="92">
+    <row r="92" spans="1:18" s="157" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="29">
         <v>91</v>
       </c>
-      <c r="B92" s="161" t="s">
+      <c r="B92" s="153" t="s">
         <v>1209</v>
       </c>
-      <c r="C92" s="162" t="s">
+      <c r="C92" s="154" t="s">
         <v>1210</v>
       </c>
-      <c r="D92" s="163" t="s">
+      <c r="D92" s="155" t="s">
         <v>572</v>
       </c>
-      <c r="E92" s="92" t="s">
+      <c r="E92" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="F92" s="164" t="s">
+      <c r="F92" s="156" t="s">
         <v>1859</v>
       </c>
-      <c r="G92" s="164" t="s">
+      <c r="G92" s="156" t="s">
         <v>1860</v>
       </c>
-      <c r="H92" s="164" t="s">
+      <c r="H92" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I92" s="164"/>
-      <c r="J92" s="164" t="s">
+      <c r="I92" s="156"/>
+      <c r="J92" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K92" s="164" t="s">
+      <c r="K92" s="156" t="s">
         <v>1861</v>
       </c>
-      <c r="L92" s="163"/>
-      <c r="M92" s="163" t="s">
+      <c r="L92" s="155"/>
+      <c r="M92" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N92" s="164" t="s">
+      <c r="N92" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O92" s="164"/>
-      <c r="P92" s="164"/>
-      <c r="Q92" s="164" t="s">
+      <c r="O92" s="156"/>
+      <c r="P92" s="156"/>
+      <c r="Q92" s="156" t="s">
         <v>1862</v>
       </c>
-      <c r="R92" s="164"/>
-    </row>
-    <row r="93" spans="1:18" s="159" customFormat="1" ht="172.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R92" s="156"/>
+    </row>
+    <row r="93" spans="1:18" s="157" customFormat="1" ht="172.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="29">
         <v>92</v>
       </c>
-      <c r="B93" s="150" t="s">
+      <c r="B93" s="153" t="s">
         <v>1218</v>
       </c>
-      <c r="C93" s="151" t="s">
+      <c r="C93" s="154" t="s">
         <v>1210</v>
       </c>
-      <c r="D93" s="152" t="s">
+      <c r="D93" s="155" t="s">
         <v>575</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="E93" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F93" s="158" t="s">
+      <c r="F93" s="156" t="s">
         <v>1863</v>
       </c>
-      <c r="G93" s="158" t="s">
+      <c r="G93" s="156" t="s">
         <v>1864</v>
       </c>
-      <c r="H93" s="158" t="s">
+      <c r="H93" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I93" s="158"/>
-      <c r="J93" s="158" t="s">
+      <c r="I93" s="156"/>
+      <c r="J93" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K93" s="158" t="s">
+      <c r="K93" s="156" t="s">
         <v>1865</v>
       </c>
-      <c r="L93" s="152"/>
-      <c r="M93" s="152" t="s">
+      <c r="L93" s="155"/>
+      <c r="M93" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N93" s="158" t="s">
+      <c r="N93" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O93" s="158"/>
-      <c r="P93" s="158"/>
-      <c r="Q93" s="158" t="s">
+      <c r="O93" s="156"/>
+      <c r="P93" s="156"/>
+      <c r="Q93" s="156" t="s">
         <v>1866</v>
       </c>
-      <c r="R93" s="158"/>
-    </row>
-    <row r="94" spans="1:18" s="159" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R93" s="156"/>
+    </row>
+    <row r="94" spans="1:18" s="157" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="29">
         <v>93</v>
       </c>
-      <c r="B94" s="150" t="s">
+      <c r="B94" s="153" t="s">
         <v>1225</v>
       </c>
-      <c r="C94" s="151" t="s">
+      <c r="C94" s="154" t="s">
         <v>1210</v>
       </c>
-      <c r="D94" s="152" t="s">
+      <c r="D94" s="155" t="s">
         <v>575</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="E94" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F94" s="158" t="s">
+      <c r="F94" s="156" t="s">
         <v>1867</v>
       </c>
-      <c r="G94" s="158" t="s">
+      <c r="G94" s="156" t="s">
         <v>1868</v>
       </c>
-      <c r="H94" s="158" t="s">
+      <c r="H94" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I94" s="158"/>
-      <c r="J94" s="158" t="s">
+      <c r="I94" s="156"/>
+      <c r="J94" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K94" s="158" t="s">
+      <c r="K94" s="156" t="s">
         <v>1869</v>
       </c>
-      <c r="L94" s="152"/>
-      <c r="M94" s="152" t="s">
+      <c r="L94" s="155"/>
+      <c r="M94" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N94" s="158" t="s">
+      <c r="N94" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O94" s="158"/>
-      <c r="P94" s="158"/>
-      <c r="Q94" s="158" t="s">
+      <c r="O94" s="156"/>
+      <c r="P94" s="156"/>
+      <c r="Q94" s="156" t="s">
         <v>1870</v>
       </c>
-      <c r="R94" s="158"/>
-    </row>
-    <row r="95" spans="1:18" s="159" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R94" s="156"/>
+    </row>
+    <row r="95" spans="1:18" s="157" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="29">
         <v>94</v>
       </c>
-      <c r="B95" s="150" t="s">
+      <c r="B95" s="153" t="s">
         <v>1231</v>
       </c>
-      <c r="C95" s="151" t="s">
+      <c r="C95" s="154" t="s">
         <v>1210</v>
       </c>
-      <c r="D95" s="152" t="s">
+      <c r="D95" s="155" t="s">
         <v>575</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E95" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F95" s="158" t="s">
+      <c r="F95" s="156" t="s">
         <v>1871</v>
       </c>
-      <c r="G95" s="158" t="s">
+      <c r="G95" s="156" t="s">
         <v>1872</v>
       </c>
-      <c r="H95" s="158" t="s">
+      <c r="H95" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I95" s="158"/>
-      <c r="J95" s="158" t="s">
+      <c r="I95" s="156"/>
+      <c r="J95" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K95" s="158" t="s">
+      <c r="K95" s="156" t="s">
         <v>1873</v>
       </c>
-      <c r="L95" s="152"/>
-      <c r="M95" s="152" t="s">
+      <c r="L95" s="155"/>
+      <c r="M95" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N95" s="158" t="s">
+      <c r="N95" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O95" s="158"/>
-      <c r="P95" s="158"/>
-      <c r="Q95" s="158" t="s">
+      <c r="O95" s="156"/>
+      <c r="P95" s="156"/>
+      <c r="Q95" s="156" t="s">
         <v>1874</v>
       </c>
-      <c r="R95" s="158"/>
-    </row>
-    <row r="96" spans="1:18" s="159" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R95" s="156"/>
+    </row>
+    <row r="96" spans="1:18" s="157" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="29">
         <v>95</v>
       </c>
-      <c r="B96" s="150" t="s">
+      <c r="B96" s="153" t="s">
         <v>1236</v>
       </c>
-      <c r="C96" s="151" t="s">
+      <c r="C96" s="154" t="s">
         <v>1210</v>
       </c>
-      <c r="D96" s="152" t="s">
+      <c r="D96" s="155" t="s">
         <v>575</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E96" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F96" s="158" t="s">
+      <c r="F96" s="156" t="s">
         <v>1875</v>
       </c>
-      <c r="G96" s="158" t="s">
+      <c r="G96" s="156" t="s">
         <v>1876</v>
       </c>
-      <c r="H96" s="158" t="s">
+      <c r="H96" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I96" s="158"/>
-      <c r="J96" s="158" t="s">
+      <c r="I96" s="156"/>
+      <c r="J96" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K96" s="158" t="s">
+      <c r="K96" s="156" t="s">
         <v>1877</v>
       </c>
-      <c r="L96" s="152"/>
-      <c r="M96" s="152" t="s">
+      <c r="L96" s="155"/>
+      <c r="M96" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N96" s="158" t="s">
+      <c r="N96" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O96" s="158"/>
-      <c r="P96" s="158"/>
-      <c r="Q96" s="158" t="s">
+      <c r="O96" s="156"/>
+      <c r="P96" s="156"/>
+      <c r="Q96" s="156" t="s">
         <v>1878</v>
       </c>
-      <c r="R96" s="158"/>
-    </row>
-    <row r="97" spans="1:18" s="159" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R96" s="156"/>
+    </row>
+    <row r="97" spans="1:18" s="157" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="29">
         <v>96</v>
       </c>
-      <c r="B97" s="150" t="s">
+      <c r="B97" s="153" t="s">
         <v>1242</v>
       </c>
-      <c r="C97" s="151" t="s">
+      <c r="C97" s="154" t="s">
         <v>1210</v>
       </c>
-      <c r="D97" s="152" t="s">
+      <c r="D97" s="155" t="s">
         <v>575</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E97" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F97" s="158" t="s">
+      <c r="F97" s="156" t="s">
         <v>1879</v>
       </c>
-      <c r="G97" s="158" t="s">
+      <c r="G97" s="156" t="s">
         <v>1880</v>
       </c>
-      <c r="H97" s="158" t="s">
+      <c r="H97" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I97" s="158"/>
-      <c r="J97" s="158" t="s">
+      <c r="I97" s="156"/>
+      <c r="J97" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K97" s="158" t="s">
+      <c r="K97" s="156" t="s">
         <v>1881</v>
       </c>
-      <c r="L97" s="152"/>
-      <c r="M97" s="152" t="s">
+      <c r="L97" s="155"/>
+      <c r="M97" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N97" s="158" t="s">
+      <c r="N97" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O97" s="158"/>
-      <c r="P97" s="158"/>
-      <c r="Q97" s="158" t="s">
+      <c r="O97" s="156"/>
+      <c r="P97" s="156"/>
+      <c r="Q97" s="156" t="s">
         <v>1882</v>
       </c>
-      <c r="R97" s="158"/>
-    </row>
-    <row r="98" spans="1:18" s="159" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R97" s="156"/>
+    </row>
+    <row r="98" spans="1:18" s="157" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="29">
         <v>97</v>
       </c>
-      <c r="B98" s="150" t="s">
+      <c r="B98" s="153" t="s">
         <v>1247</v>
       </c>
-      <c r="C98" s="151" t="s">
+      <c r="C98" s="154" t="s">
         <v>1210</v>
       </c>
-      <c r="D98" s="152" t="s">
+      <c r="D98" s="155" t="s">
         <v>569</v>
       </c>
-      <c r="E98" s="2" t="s">
+      <c r="E98" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F98" s="158" t="s">
+      <c r="F98" s="156" t="s">
         <v>1883</v>
       </c>
-      <c r="G98" s="158" t="s">
+      <c r="G98" s="156" t="s">
         <v>1884</v>
       </c>
-      <c r="H98" s="158" t="s">
+      <c r="H98" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I98" s="158"/>
-      <c r="J98" s="158" t="s">
+      <c r="I98" s="156"/>
+      <c r="J98" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K98" s="158" t="s">
+      <c r="K98" s="156" t="s">
         <v>1885</v>
       </c>
-      <c r="L98" s="152"/>
-      <c r="M98" s="152" t="s">
+      <c r="L98" s="155"/>
+      <c r="M98" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N98" s="158" t="s">
+      <c r="N98" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O98" s="158"/>
-      <c r="P98" s="158"/>
-      <c r="Q98" s="158" t="s">
+      <c r="O98" s="156"/>
+      <c r="P98" s="156"/>
+      <c r="Q98" s="156" t="s">
         <v>1886</v>
       </c>
-      <c r="R98" s="158"/>
-    </row>
-    <row r="99" spans="1:18" s="159" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R98" s="156"/>
+    </row>
+    <row r="99" spans="1:18" s="157" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="29">
         <v>98</v>
       </c>
-      <c r="B99" s="150" t="s">
+      <c r="B99" s="153" t="s">
         <v>1252</v>
       </c>
-      <c r="C99" s="151" t="s">
+      <c r="C99" s="154" t="s">
         <v>1210</v>
       </c>
-      <c r="D99" s="152" t="s">
+      <c r="D99" s="155" t="s">
         <v>575</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="E99" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F99" s="158" t="s">
+      <c r="F99" s="156" t="s">
         <v>1887</v>
       </c>
-      <c r="G99" s="158" t="s">
+      <c r="G99" s="156" t="s">
         <v>1888</v>
       </c>
-      <c r="H99" s="158" t="s">
+      <c r="H99" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I99" s="158"/>
-      <c r="J99" s="158" t="s">
+      <c r="I99" s="156"/>
+      <c r="J99" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K99" s="158" t="s">
+      <c r="K99" s="156" t="s">
         <v>1889</v>
       </c>
-      <c r="L99" s="152"/>
-      <c r="M99" s="152" t="s">
+      <c r="L99" s="155"/>
+      <c r="M99" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N99" s="158" t="s">
+      <c r="N99" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O99" s="158"/>
-      <c r="P99" s="158"/>
-      <c r="Q99" s="158" t="s">
+      <c r="O99" s="156"/>
+      <c r="P99" s="156"/>
+      <c r="Q99" s="156" t="s">
         <v>1890</v>
       </c>
-      <c r="R99" s="158"/>
-    </row>
-    <row r="100" spans="1:18" s="159" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R99" s="156"/>
+    </row>
+    <row r="100" spans="1:18" s="157" customFormat="1" ht="144" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="29">
         <v>99</v>
       </c>
-      <c r="B100" s="150" t="s">
+      <c r="B100" s="153" t="s">
         <v>1258</v>
       </c>
-      <c r="C100" s="151" t="s">
+      <c r="C100" s="154" t="s">
         <v>1210</v>
       </c>
-      <c r="D100" s="152" t="s">
+      <c r="D100" s="155" t="s">
         <v>575</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="E100" s="29" t="s">
         <v>1891</v>
       </c>
-      <c r="F100" s="158" t="s">
+      <c r="F100" s="156" t="s">
         <v>1892</v>
       </c>
-      <c r="G100" s="158" t="s">
+      <c r="G100" s="156" t="s">
         <v>1893</v>
       </c>
-      <c r="H100" s="158" t="s">
+      <c r="H100" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I100" s="158"/>
-      <c r="J100" s="158" t="s">
+      <c r="I100" s="156"/>
+      <c r="J100" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K100" s="158" t="s">
+      <c r="K100" s="156" t="s">
         <v>1894</v>
       </c>
-      <c r="L100" s="152"/>
-      <c r="M100" s="152" t="s">
+      <c r="L100" s="155"/>
+      <c r="M100" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N100" s="158" t="s">
+      <c r="N100" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O100" s="158"/>
-      <c r="P100" s="158"/>
-      <c r="Q100" s="158" t="s">
+      <c r="O100" s="156"/>
+      <c r="P100" s="156"/>
+      <c r="Q100" s="156" t="s">
         <v>1895</v>
       </c>
-      <c r="R100" s="158"/>
-    </row>
-    <row r="101" spans="1:18" s="159" customFormat="1" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R100" s="156"/>
+    </row>
+    <row r="101" spans="1:18" s="157" customFormat="1" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="29">
         <v>100</v>
       </c>
-      <c r="B101" s="150" t="s">
+      <c r="B101" s="153" t="s">
         <v>1265</v>
       </c>
-      <c r="C101" s="151" t="s">
+      <c r="C101" s="154" t="s">
         <v>1210</v>
       </c>
-      <c r="D101" s="152" t="s">
+      <c r="D101" s="155" t="s">
         <v>575</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="E101" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F101" s="158" t="s">
+      <c r="F101" s="156" t="s">
         <v>1896</v>
       </c>
-      <c r="G101" s="158" t="s">
+      <c r="G101" s="156" t="s">
         <v>1897</v>
       </c>
-      <c r="H101" s="158" t="s">
+      <c r="H101" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I101" s="158"/>
-      <c r="J101" s="158" t="s">
+      <c r="I101" s="156"/>
+      <c r="J101" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K101" s="158" t="s">
+      <c r="K101" s="156" t="s">
         <v>1898</v>
       </c>
-      <c r="L101" s="152"/>
-      <c r="M101" s="152" t="s">
+      <c r="L101" s="155"/>
+      <c r="M101" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N101" s="158" t="s">
+      <c r="N101" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O101" s="158"/>
-      <c r="P101" s="158"/>
-      <c r="Q101" s="158" t="s">
+      <c r="O101" s="156"/>
+      <c r="P101" s="156"/>
+      <c r="Q101" s="156" t="s">
         <v>1899</v>
       </c>
-      <c r="R101" s="158"/>
-    </row>
-    <row r="102" spans="1:18" s="159" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R101" s="156"/>
+    </row>
+    <row r="102" spans="1:18" s="157" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="29">
         <v>101</v>
       </c>
-      <c r="B102" s="150" t="s">
+      <c r="B102" s="153" t="s">
         <v>1269</v>
       </c>
-      <c r="C102" s="151" t="s">
+      <c r="C102" s="154" t="s">
         <v>1210</v>
       </c>
-      <c r="D102" s="152" t="s">
+      <c r="D102" s="155" t="s">
         <v>578</v>
       </c>
-      <c r="E102" s="2" t="s">
+      <c r="E102" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F102" s="158" t="s">
+      <c r="F102" s="156" t="s">
         <v>1900</v>
       </c>
-      <c r="G102" s="158" t="s">
+      <c r="G102" s="156" t="s">
         <v>1476</v>
       </c>
-      <c r="H102" s="158" t="s">
+      <c r="H102" s="156" t="s">
         <v>1563</v>
       </c>
-      <c r="I102" s="158" t="s">
+      <c r="I102" s="156" t="s">
         <v>1901</v>
       </c>
-      <c r="J102" s="158"/>
-      <c r="K102" s="158" t="s">
+      <c r="J102" s="156"/>
+      <c r="K102" s="156" t="s">
         <v>1902</v>
       </c>
-      <c r="L102" s="152"/>
-      <c r="M102" s="152" t="s">
+      <c r="L102" s="155"/>
+      <c r="M102" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N102" s="158" t="s">
+      <c r="N102" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O102" s="158"/>
-      <c r="P102" s="158"/>
-      <c r="Q102" s="158" t="s">
+      <c r="O102" s="156"/>
+      <c r="P102" s="156"/>
+      <c r="Q102" s="156" t="s">
         <v>1903</v>
       </c>
-      <c r="R102" s="158"/>
-    </row>
-    <row r="103" spans="1:18" s="159" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R102" s="156"/>
+    </row>
+    <row r="103" spans="1:18" s="157" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="29">
         <v>102</v>
       </c>
-      <c r="B103" s="150" t="s">
+      <c r="B103" s="153" t="s">
         <v>1275</v>
       </c>
-      <c r="C103" s="151" t="s">
+      <c r="C103" s="154" t="s">
         <v>1276</v>
       </c>
-      <c r="D103" s="152" t="s">
+      <c r="D103" s="155" t="s">
         <v>569</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="E103" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="F103" s="158" t="s">
+      <c r="F103" s="156" t="s">
         <v>1904</v>
       </c>
-      <c r="G103" s="158" t="s">
+      <c r="G103" s="156" t="s">
         <v>1905</v>
       </c>
-      <c r="H103" s="158" t="s">
+      <c r="H103" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I103" s="158"/>
-      <c r="J103" s="158" t="s">
+      <c r="I103" s="156"/>
+      <c r="J103" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K103" s="158" t="s">
+      <c r="K103" s="156" t="s">
         <v>1906</v>
       </c>
-      <c r="L103" s="152"/>
-      <c r="M103" s="152" t="s">
+      <c r="L103" s="155"/>
+      <c r="M103" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N103" s="158" t="s">
+      <c r="N103" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O103" s="158"/>
-      <c r="P103" s="158"/>
-      <c r="Q103" s="158" t="s">
+      <c r="O103" s="156"/>
+      <c r="P103" s="156"/>
+      <c r="Q103" s="156" t="s">
         <v>1907</v>
       </c>
-      <c r="R103" s="158"/>
-    </row>
-    <row r="104" spans="1:18" s="159" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R103" s="156"/>
+    </row>
+    <row r="104" spans="1:18" s="157" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="29">
         <v>103</v>
       </c>
-      <c r="B104" s="150" t="s">
+      <c r="B104" s="153" t="s">
         <v>1281</v>
       </c>
-      <c r="C104" s="151" t="s">
+      <c r="C104" s="154" t="s">
         <v>1276</v>
       </c>
-      <c r="D104" s="152" t="s">
+      <c r="D104" s="155" t="s">
         <v>569</v>
       </c>
-      <c r="E104" s="2" t="s">
+      <c r="E104" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F104" s="158" t="s">
+      <c r="F104" s="156" t="s">
         <v>1908</v>
       </c>
-      <c r="G104" s="158" t="s">
+      <c r="G104" s="156" t="s">
         <v>1909</v>
       </c>
-      <c r="H104" s="158" t="s">
+      <c r="H104" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I104" s="158"/>
-      <c r="J104" s="158" t="s">
+      <c r="I104" s="156"/>
+      <c r="J104" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K104" s="158" t="s">
+      <c r="K104" s="156" t="s">
         <v>1910</v>
       </c>
-      <c r="L104" s="152"/>
-      <c r="M104" s="152" t="s">
+      <c r="L104" s="155"/>
+      <c r="M104" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N104" s="158" t="s">
+      <c r="N104" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O104" s="158"/>
-      <c r="P104" s="158"/>
-      <c r="Q104" s="158" t="s">
+      <c r="O104" s="156"/>
+      <c r="P104" s="156"/>
+      <c r="Q104" s="156" t="s">
         <v>1911</v>
       </c>
-      <c r="R104" s="158"/>
-    </row>
-    <row r="105" spans="1:18" s="159" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R104" s="156"/>
+    </row>
+    <row r="105" spans="1:18" s="157" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="29">
         <v>104</v>
       </c>
-      <c r="B105" s="150" t="s">
+      <c r="B105" s="153" t="s">
         <v>1285</v>
       </c>
-      <c r="C105" s="151" t="s">
+      <c r="C105" s="154" t="s">
         <v>1276</v>
       </c>
-      <c r="D105" s="152" t="s">
+      <c r="D105" s="155" t="s">
         <v>578</v>
       </c>
-      <c r="E105" s="2" t="s">
+      <c r="E105" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F105" s="158" t="s">
+      <c r="F105" s="156" t="s">
         <v>1912</v>
       </c>
-      <c r="G105" s="158" t="s">
+      <c r="G105" s="156" t="s">
         <v>1476</v>
       </c>
-      <c r="H105" s="158" t="s">
+      <c r="H105" s="156" t="s">
         <v>1563</v>
       </c>
-      <c r="I105" s="158" t="s">
+      <c r="I105" s="156" t="s">
         <v>1913</v>
       </c>
-      <c r="J105" s="158"/>
-      <c r="K105" s="158" t="s">
+      <c r="J105" s="156"/>
+      <c r="K105" s="156" t="s">
         <v>1914</v>
       </c>
-      <c r="L105" s="152"/>
-      <c r="M105" s="152" t="s">
+      <c r="L105" s="155"/>
+      <c r="M105" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N105" s="158" t="s">
+      <c r="N105" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O105" s="158"/>
-      <c r="P105" s="158"/>
-      <c r="Q105" s="158" t="s">
+      <c r="O105" s="156"/>
+      <c r="P105" s="156"/>
+      <c r="Q105" s="156" t="s">
         <v>1915</v>
       </c>
-      <c r="R105" s="158"/>
-    </row>
-    <row r="106" spans="1:18" s="159" customFormat="1" ht="150.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" s="158">
+      <c r="R105" s="156"/>
+    </row>
+    <row r="106" spans="1:18" s="157" customFormat="1" ht="150.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="156">
         <v>105</v>
       </c>
       <c r="B106" s="160" t="s">
         <v>1289</v>
       </c>
-      <c r="C106" s="158" t="s">
+      <c r="C106" s="156" t="s">
         <v>1193</v>
       </c>
-      <c r="D106" s="158" t="s">
+      <c r="D106" s="156" t="s">
         <v>1290</v>
       </c>
-      <c r="E106" s="158" t="s">
+      <c r="E106" s="156" t="s">
         <v>1916</v>
       </c>
-      <c r="F106" s="158" t="s">
+      <c r="F106" s="156" t="s">
         <v>1917</v>
       </c>
-      <c r="G106" s="158" t="s">
+      <c r="G106" s="156" t="s">
         <v>1918</v>
       </c>
-      <c r="H106" s="158" t="s">
+      <c r="H106" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I106" s="158"/>
-      <c r="J106" s="158" t="s">
+      <c r="I106" s="156"/>
+      <c r="J106" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K106" s="158" t="s">
+      <c r="K106" s="156" t="s">
         <v>1919</v>
       </c>
-      <c r="L106" s="158"/>
-      <c r="M106" s="158" t="s">
+      <c r="L106" s="156"/>
+      <c r="M106" s="156" t="s">
         <v>1559</v>
       </c>
-      <c r="N106" s="158" t="s">
+      <c r="N106" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O106" s="158"/>
-      <c r="P106" s="158" t="s">
+      <c r="O106" s="156"/>
+      <c r="P106" s="156" t="s">
         <v>1920</v>
       </c>
-      <c r="Q106" s="158" t="s">
+      <c r="Q106" s="156" t="s">
         <v>1921</v>
       </c>
-      <c r="R106" s="158"/>
-    </row>
-    <row r="107" spans="1:18" s="159" customFormat="1" ht="201.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R106" s="156"/>
+    </row>
+    <row r="107" spans="1:18" s="157" customFormat="1" ht="201.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="29">
         <v>106</v>
       </c>
-      <c r="B107" s="150" t="s">
+      <c r="B107" s="153" t="s">
         <v>1161</v>
       </c>
-      <c r="C107" s="151" t="s">
+      <c r="C107" s="154" t="s">
         <v>1162</v>
       </c>
-      <c r="D107" s="152" t="s">
+      <c r="D107" s="155" t="s">
         <v>578</v>
       </c>
-      <c r="E107" s="2"/>
-      <c r="F107" s="158" t="s">
+      <c r="E107" s="29"/>
+      <c r="F107" s="156" t="s">
         <v>1922</v>
       </c>
-      <c r="G107" s="158" t="s">
+      <c r="G107" s="156" t="s">
         <v>1476</v>
       </c>
-      <c r="H107" s="158"/>
-      <c r="I107" s="158" t="s">
+      <c r="H107" s="156"/>
+      <c r="I107" s="156" t="s">
         <v>1923</v>
       </c>
-      <c r="J107" s="158" t="s">
-        <v>1433</v>
-      </c>
-      <c r="K107" s="158" t="s">
+      <c r="J107" s="156" t="s">
+        <v>1433</v>
+      </c>
+      <c r="K107" s="156" t="s">
         <v>1924</v>
       </c>
-      <c r="L107" s="152"/>
-      <c r="M107" s="152"/>
-      <c r="N107" s="158" t="s">
+      <c r="L107" s="155"/>
+      <c r="M107" s="155"/>
+      <c r="N107" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O107" s="158" t="s">
-        <v>1433</v>
-      </c>
-      <c r="P107" s="158" t="s">
+      <c r="O107" s="156" t="s">
+        <v>1433</v>
+      </c>
+      <c r="P107" s="156" t="s">
         <v>1925</v>
       </c>
-      <c r="Q107" s="158" t="s">
+      <c r="Q107" s="156" t="s">
         <v>1926</v>
       </c>
-      <c r="R107" s="158" t="s">
-        <v>1433</v>
-      </c>
-    </row>
-    <row r="108" spans="1:18" s="159" customFormat="1" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R107" s="156" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" s="157" customFormat="1" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="29">
         <v>107</v>
       </c>
-      <c r="B108" s="150" t="s">
+      <c r="B108" s="153" t="s">
         <v>1168</v>
       </c>
-      <c r="C108" s="151" t="s">
+      <c r="C108" s="154" t="s">
         <v>1162</v>
       </c>
-      <c r="D108" s="152" t="s">
+      <c r="D108" s="155" t="s">
         <v>569</v>
       </c>
-      <c r="E108" s="2"/>
-      <c r="F108" s="158" t="s">
+      <c r="E108" s="29"/>
+      <c r="F108" s="156" t="s">
         <v>1927</v>
       </c>
-      <c r="G108" s="158" t="s">
+      <c r="G108" s="156" t="s">
         <v>1928</v>
       </c>
-      <c r="H108" s="158" t="s">
+      <c r="H108" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I108" s="158" t="s">
-        <v>1433</v>
-      </c>
-      <c r="J108" s="158" t="s">
+      <c r="I108" s="156" t="s">
+        <v>1433</v>
+      </c>
+      <c r="J108" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K108" s="158" t="s">
+      <c r="K108" s="156" t="s">
         <v>1929</v>
       </c>
-      <c r="L108" s="152"/>
-      <c r="M108" s="152"/>
-      <c r="N108" s="158" t="s">
+      <c r="L108" s="155"/>
+      <c r="M108" s="155"/>
+      <c r="N108" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O108" s="158" t="s">
-        <v>1433</v>
-      </c>
-      <c r="P108" s="158" t="s">
-        <v>1433</v>
-      </c>
-      <c r="Q108" s="158" t="s">
+      <c r="O108" s="156" t="s">
+        <v>1433</v>
+      </c>
+      <c r="P108" s="156" t="s">
+        <v>1433</v>
+      </c>
+      <c r="Q108" s="156" t="s">
         <v>1930</v>
       </c>
-      <c r="R108" s="158" t="s">
-        <v>1433</v>
-      </c>
-    </row>
-    <row r="109" spans="1:18" s="159" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R108" s="156" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" s="157" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="29">
         <v>108</v>
       </c>
-      <c r="B109" s="150" t="s">
+      <c r="B109" s="153" t="s">
         <v>1296</v>
       </c>
-      <c r="C109" s="151" t="s">
+      <c r="C109" s="154" t="s">
         <v>1297</v>
       </c>
-      <c r="D109" s="152" t="s">
+      <c r="D109" s="155" t="s">
         <v>572</v>
       </c>
       <c r="E109" s="160" t="s">
         <v>285</v>
       </c>
-      <c r="F109" s="158" t="s">
+      <c r="F109" s="156" t="s">
         <v>1931</v>
       </c>
-      <c r="G109" s="158" t="s">
+      <c r="G109" s="156" t="s">
         <v>1932</v>
       </c>
-      <c r="H109" s="158" t="s">
+      <c r="H109" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I109" s="158"/>
-      <c r="J109" s="158" t="s">
+      <c r="I109" s="156"/>
+      <c r="J109" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K109" s="158" t="s">
+      <c r="K109" s="156" t="s">
         <v>1933</v>
       </c>
-      <c r="L109" s="152"/>
-      <c r="M109" s="152" t="s">
+      <c r="L109" s="155"/>
+      <c r="M109" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N109" s="158" t="s">
+      <c r="N109" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O109" s="158"/>
-      <c r="P109" s="158"/>
-      <c r="Q109" s="158" t="s">
+      <c r="O109" s="156"/>
+      <c r="P109" s="156"/>
+      <c r="Q109" s="156" t="s">
         <v>1934</v>
       </c>
-      <c r="R109" s="158"/>
-    </row>
-    <row r="110" spans="1:18" s="159" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R109" s="156"/>
+    </row>
+    <row r="110" spans="1:18" s="157" customFormat="1" ht="100.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="29">
         <v>109</v>
       </c>
-      <c r="B110" s="150" t="s">
+      <c r="B110" s="153" t="s">
         <v>1304</v>
       </c>
-      <c r="C110" s="151" t="s">
+      <c r="C110" s="154" t="s">
         <v>1297</v>
       </c>
-      <c r="D110" s="152" t="s">
+      <c r="D110" s="155" t="s">
         <v>569</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="E110" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F110" s="158" t="s">
+      <c r="F110" s="156" t="s">
         <v>1935</v>
       </c>
-      <c r="G110" s="158" t="s">
+      <c r="G110" s="156" t="s">
         <v>1936</v>
       </c>
-      <c r="H110" s="158" t="s">
+      <c r="H110" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I110" s="158"/>
-      <c r="J110" s="158" t="s">
+      <c r="I110" s="156"/>
+      <c r="J110" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K110" s="158" t="s">
+      <c r="K110" s="156" t="s">
         <v>1937</v>
       </c>
-      <c r="L110" s="152"/>
-      <c r="M110" s="152" t="s">
+      <c r="L110" s="155"/>
+      <c r="M110" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N110" s="158" t="s">
+      <c r="N110" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O110" s="158"/>
-      <c r="P110" s="158"/>
-      <c r="Q110" s="158" t="s">
+      <c r="O110" s="156"/>
+      <c r="P110" s="156"/>
+      <c r="Q110" s="156" t="s">
         <v>1938</v>
       </c>
-      <c r="R110" s="158"/>
-    </row>
-    <row r="111" spans="1:18" s="159" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="R110" s="156"/>
+    </row>
+    <row r="111" spans="1:18" s="157" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="29">
         <v>110</v>
       </c>
-      <c r="B111" s="150" t="s">
+      <c r="B111" s="153" t="s">
         <v>1310</v>
       </c>
-      <c r="C111" s="151" t="s">
+      <c r="C111" s="154" t="s">
         <v>1297</v>
       </c>
-      <c r="D111" s="152" t="s">
+      <c r="D111" s="155" t="s">
         <v>569</v>
       </c>
-      <c r="E111" s="2" t="s">
+      <c r="E111" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="F111" s="158" t="s">
+      <c r="F111" s="156" t="s">
         <v>1939</v>
       </c>
-      <c r="G111" s="158" t="s">
+      <c r="G111" s="156" t="s">
         <v>1940</v>
       </c>
-      <c r="H111" s="158" t="s">
+      <c r="H111" s="156" t="s">
         <v>1441</v>
       </c>
-      <c r="I111" s="158"/>
-      <c r="J111" s="158" t="s">
+      <c r="I111" s="156"/>
+      <c r="J111" s="156" t="s">
         <v>1442</v>
       </c>
-      <c r="K111" s="158" t="s">
+      <c r="K111" s="156" t="s">
         <v>1941</v>
       </c>
-      <c r="L111" s="152"/>
-      <c r="M111" s="152" t="s">
+      <c r="L111" s="155"/>
+      <c r="M111" s="155" t="s">
         <v>1559</v>
       </c>
-      <c r="N111" s="158" t="s">
+      <c r="N111" s="156" t="s">
         <v>1437</v>
       </c>
-      <c r="O111" s="158"/>
-      <c r="P111" s="158"/>
-      <c r="Q111" s="158" t="s">
+      <c r="O111" s="156"/>
+      <c r="P111" s="156"/>
+      <c r="Q111" s="156" t="s">
         <v>1942</v>
       </c>
-      <c r="R111" s="158"/>
-    </row>
-    <row r="112" spans="1:18" s="159" customFormat="1" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" s="29">
+      <c r="R111" s="156"/>
+    </row>
+    <row r="112" spans="1:18" s="166" customFormat="1" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="161">
         <v>111</v>
       </c>
-      <c r="B112" s="150" t="s">
+      <c r="B112" s="162" t="s">
         <v>1315</v>
       </c>
-      <c r="C112" s="151" t="s">
+      <c r="C112" s="163" t="s">
         <v>1316</v>
       </c>
-      <c r="D112" s="152" t="s">
+      <c r="D112" s="164" t="s">
         <v>572</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="E112" s="161" t="s">
         <v>289</v>
       </c>
-      <c r="F112" s="158" t="s">
+      <c r="F112" s="165" t="s">
         <v>1943</v>
       </c>
-      <c r="G112" s="158" t="s">
+      <c r="G112" s="165" t="s">
         <v>1944</v>
       </c>
-      <c r="H112" s="158" t="s">
+      <c r="H112" s="165" t="s">
         <v>1441</v>
       </c>
-      <c r="I112" s="158"/>
-      <c r="J112" s="158" t="s">
+      <c r="I112" s="165"/>
+      <c r="J112" s="165" t="s">
         <v>1442</v>
       </c>
-      <c r="K112" s="158" t="s">
+      <c r="K112" s="165" t="s">
         <v>1945</v>
       </c>
-      <c r="L112" s="152"/>
-      <c r="M112" s="152" t="s">
+      <c r="L112" s="164"/>
+      <c r="M112" s="164" t="s">
         <v>1559</v>
       </c>
-      <c r="N112" s="158" t="s">
+      <c r="N112" s="165" t="s">
         <v>1437</v>
       </c>
-      <c r="O112" s="158"/>
-      <c r="P112" s="158"/>
-      <c r="Q112" s="158" t="s">
+      <c r="O112" s="165"/>
+      <c r="P112" s="165"/>
+      <c r="Q112" s="165" t="s">
         <v>1946</v>
       </c>
-      <c r="R112" s="158"/>
+      <c r="R112" s="165"/>
     </row>
     <row r="113" spans="1:18" s="159" customFormat="1" ht="115.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="29">
